--- a/data/GTO__LIST_OF_ITEMS.xlsx
+++ b/data/GTO__LIST_OF_ITEMS.xlsx
@@ -2300,7 +2300,7 @@
     <t>Contrato: ICN_SBR</t>
   </si>
   <si>
-    <t>Gerado em 27/7/2026 às 10:42</t>
+    <t>Gerado em 27/7/2026 às 11:52</t>
   </si>
 </sst>
 </file>
